--- a/output/top_per_year.xlsx
+++ b/output/top_per_year.xlsx
@@ -428,57 +428,57 @@
   <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
-    <col width="24" customWidth="1" min="27" max="27"/>
-    <col width="24" customWidth="1" min="28" max="28"/>
-    <col width="24" customWidth="1" min="29" max="29"/>
-    <col width="24" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="24" customWidth="1" min="33" max="33"/>
-    <col width="24" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
-    <col width="24" customWidth="1" min="37" max="37"/>
-    <col width="24" customWidth="1" min="38" max="38"/>
-    <col width="24" customWidth="1" min="39" max="39"/>
-    <col width="24" customWidth="1" min="40" max="40"/>
-    <col width="24" customWidth="1" min="41" max="41"/>
-    <col width="24" customWidth="1" min="42" max="42"/>
-    <col width="24" customWidth="1" min="43" max="43"/>
-    <col width="24" customWidth="1" min="44" max="44"/>
-    <col width="24" customWidth="1" min="45" max="45"/>
-    <col width="24" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
-    <col width="24" customWidth="1" min="48" max="48"/>
-    <col width="24" customWidth="1" min="49" max="49"/>
-    <col width="24" customWidth="1" min="50" max="50"/>
-    <col width="24" customWidth="1" min="51" max="51"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="25" customWidth="1" min="29" max="29"/>
+    <col width="25" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="33" max="33"/>
+    <col width="25" customWidth="1" min="34" max="34"/>
+    <col width="25" customWidth="1" min="35" max="35"/>
+    <col width="25" customWidth="1" min="36" max="36"/>
+    <col width="25" customWidth="1" min="37" max="37"/>
+    <col width="25" customWidth="1" min="38" max="38"/>
+    <col width="25" customWidth="1" min="39" max="39"/>
+    <col width="25" customWidth="1" min="40" max="40"/>
+    <col width="25" customWidth="1" min="41" max="41"/>
+    <col width="25" customWidth="1" min="42" max="42"/>
+    <col width="25" customWidth="1" min="43" max="43"/>
+    <col width="25" customWidth="1" min="44" max="44"/>
+    <col width="25" customWidth="1" min="45" max="45"/>
+    <col width="25" customWidth="1" min="46" max="46"/>
+    <col width="25" customWidth="1" min="47" max="47"/>
+    <col width="25" customWidth="1" min="48" max="48"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="50" max="50"/>
+    <col width="25" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/output/top_per_year.xlsx
+++ b/output/top_per_year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -478,261 +478,255 @@
     <col width="25" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="25" customWidth="1" min="50" max="50"/>
-    <col width="25" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>1801</t>
         </is>
@@ -989,11 +983,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1048,205 +1037,200 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
       <c r="AX3" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
@@ -1305,205 +1289,200 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Lille (partie française)</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
       <c r="AX4" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
         <is>
           <t>Marseille-Aix-en-Provence</t>
         </is>
@@ -1517,7 +1496,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Lille (partie française)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1647,64 +1626,64 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Marseille-Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>Lille (partie française)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Marseille-Aix-en-Provence</t>
-        </is>
-      </c>
       <c r="AN5" t="inlineStr">
         <is>
           <t>Lille (partie française)</t>
@@ -1756,11 +1735,6 @@
         </is>
       </c>
       <c r="AX5" t="inlineStr">
-        <is>
-          <t>Lille (partie française)</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
         <is>
           <t>Bordeaux</t>
         </is>
@@ -1774,7 +1748,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lille (partie française)</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1814,7 +1788,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1874,12 +1848,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Douai-Lens</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Douai-Lens</t>
+          <t>Bordeaux</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1974,19 +1948,19 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>Bordeaux</t>
@@ -2013,11 +1987,6 @@
         </is>
       </c>
       <c r="AX6" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
         <is>
           <t>Lille (partie française)</t>
         </is>
@@ -2056,225 +2025,220 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
       <c r="AX7" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
@@ -2313,172 +2277,172 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>Douai-Lens</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Douai-Lens</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Avignon</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2513,7 +2477,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>Avignon</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2527,11 +2491,6 @@
         </is>
       </c>
       <c r="AX8" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
@@ -2625,152 +2584,152 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Avignon</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2784,11 +2743,6 @@
         </is>
       </c>
       <c r="AX9" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>Avignon</t>
         </is>
@@ -2882,7 +2836,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Toulon</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2897,155 +2851,150 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
       <c r="AX10" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
@@ -3139,7 +3088,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Douai-Lens</t>
+          <t>Toulon</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3149,160 +3098,155 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Toulon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AU11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
       <c r="AX11" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
@@ -3331,219 +3275,219 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>Toulon</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
@@ -3555,11 +3499,6 @@
         </is>
       </c>
       <c r="AX12" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
@@ -3568,7 +3507,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3588,7 +3527,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Strasbourg (partie française)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3653,170 +3592,165 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>Douai-Lens</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
         <is>
           <t>Douai-Lens</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>Douai-Lens</t>
         </is>
       </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
       <c r="AX13" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
         <is>
           <t>Douai-Lens</t>
         </is>
@@ -3825,7 +3759,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3835,7 +3769,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Avignon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3865,199 +3799,199 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>Avignon</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t>Toulon</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>Toulon</t>
@@ -4069,11 +4003,6 @@
         </is>
       </c>
       <c r="AX14" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
         <is>
           <t>Orléans</t>
         </is>
@@ -4092,229 +4021,229 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Avignon</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Avignon</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Avignon</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>Avignon</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AK15" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>Strasbourg (partie française)</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
         <is>
           <t>Toulon</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>Toulon</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>Nice</t>
@@ -4326,11 +4255,6 @@
         </is>
       </c>
       <c r="AX15" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
@@ -4354,7 +4278,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4419,12 +4343,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Avignon</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4434,129 +4358,129 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>Avignon</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
@@ -4569,7 +4493,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>Valenciennes (partie française)</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4583,11 +4507,6 @@
         </is>
       </c>
       <c r="AX16" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
         <is>
           <t>Toulon</t>
         </is>
@@ -4596,7 +4515,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4676,7 +4595,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Béthune</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4686,149 +4605,149 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>Béthune</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Strasbourg (partie française)</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>Strasbourg (partie française)</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
@@ -4840,11 +4759,6 @@
         </is>
       </c>
       <c r="AX17" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
         <is>
           <t>Tours</t>
         </is>
@@ -4853,7 +4767,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4868,7 +4782,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Tours</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4893,179 +4807,179 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Valenciennes (partie française)</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Toulon</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Douai-Lens</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Valenciennes (partie française)</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Toulon</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Douai-Lens</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
       <c r="AR18" t="inlineStr">
         <is>
           <t>Tours</t>
@@ -5073,7 +4987,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>Tours</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
@@ -5083,7 +4997,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5097,11 +5011,6 @@
         </is>
       </c>
       <c r="AX18" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
         <is>
           <t>Valenciennes (partie française)</t>
         </is>
@@ -5125,34 +5034,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Béthune</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Béthune</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Tours</t>
@@ -5210,155 +5119,150 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Avignon</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AK19" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
         <is>
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Avignon</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
         <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AT19" t="inlineStr">
         <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
+      <c r="AV19" t="inlineStr">
         <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>Tours</t>
         </is>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
       <c r="AX19" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
         <is>
           <t>Clermont-Ferrand</t>
         </is>
@@ -5392,7 +5296,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Béthune</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5417,7 +5321,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Valenciennes (partie française)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5452,12 +5356,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Valenciennes (partie française)</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -5477,7 +5381,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -5502,82 +5406,82 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>Brest</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -5587,7 +5491,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Clermont-Ferrand</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -5611,11 +5515,6 @@
         </is>
       </c>
       <c r="AX20" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
@@ -5674,7 +5573,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Valenciennes (partie française)</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -5709,170 +5608,165 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
           <t>Nancy</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Nîmes</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Nîmes</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>Nîmes</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr">
+      <c r="AV21" t="inlineStr">
         <is>
           <t>Nîmes</t>
         </is>
       </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Pau</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
+      <c r="AW21" t="inlineStr">
         <is>
           <t>Nîmes</t>
         </is>
       </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Nîmes</t>
-        </is>
-      </c>
       <c r="AX21" t="inlineStr">
-        <is>
-          <t>Nîmes</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
         <is>
           <t>Nîmes</t>
         </is>
@@ -5896,29 +5790,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Metz</t>
@@ -5971,139 +5865,139 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>Pau</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr">
         <is>
           <t>Pau</t>
@@ -6111,7 +6005,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6125,11 +6019,6 @@
         </is>
       </c>
       <c r="AX22" t="inlineStr">
-        <is>
-          <t>Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
         <is>
           <t>Amiens</t>
         </is>
@@ -6148,219 +6037,219 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
           <t>Orléans</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
           <t>Amiens</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>Pau</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>Pau</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>Caen</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr">
         <is>
           <t>Amiens</t>
@@ -6382,11 +6271,6 @@
         </is>
       </c>
       <c r="AX23" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
@@ -6405,227 +6289,227 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Orléans</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
         <is>
           <t>Clermont-Ferrand</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>Nîmes</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>Nîmes</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AT24" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>Nîmes</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>Nîmes</t>
-        </is>
-      </c>
-      <c r="AT24" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -6639,11 +6523,6 @@
         </is>
       </c>
       <c r="AX24" t="inlineStr">
-        <is>
-          <t>Caen</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
         <is>
           <t>Saint-Étienne</t>
         </is>
@@ -6747,160 +6626,155 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mulhouse</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
           <t>Clermont-Ferrand</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Mulhouse</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AR25" t="inlineStr">
         <is>
           <t>Brest</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Clermont-Ferrand</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AV25" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AW25" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pau</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>Caen</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>Caen</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>Caen</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
       <c r="AX25" t="inlineStr">
-        <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
         <is>
           <t>Angers</t>
         </is>
